--- a/results/cifar10_2_255_result.xlsx
+++ b/results/cifar10_2_255_result.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20380"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA8758C-FD43-41C0-99D1-A3DDD0970464}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F9F190-7846-4514-8CCA-1622F024DE13}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>image</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,14 +43,6 @@
   </si>
   <si>
     <t>BTime_NN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>new_NN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>new_SR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -376,15 +368,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="13.46484375" customWidth="1"/>
     <col min="5" max="5" width="11.73046875" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -403,14 +394,8 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -429,14 +414,8 @@
       <c r="F2">
         <v>4.3324801921844482</v>
       </c>
-      <c r="G2">
-        <v>3.86</v>
-      </c>
-      <c r="H2">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -455,14 +434,8 @@
       <c r="F3">
         <v>2.6977119445800781</v>
       </c>
-      <c r="G3">
-        <v>2.57</v>
-      </c>
-      <c r="H3">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -481,14 +454,8 @@
       <c r="F4">
         <v>55.660949230194092</v>
       </c>
-      <c r="G4">
-        <v>308.83</v>
-      </c>
-      <c r="H4">
-        <v>300.10000000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -507,14 +474,8 @@
       <c r="F5">
         <v>9.6645317077636719</v>
       </c>
-      <c r="G5">
-        <v>10.91</v>
-      </c>
-      <c r="H5">
-        <v>13.47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -533,14 +494,8 @@
       <c r="F6">
         <v>300.54827642440802</v>
       </c>
-      <c r="G6">
-        <v>300.49</v>
-      </c>
-      <c r="H6">
-        <v>300.14999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -559,14 +514,8 @@
       <c r="F7">
         <v>158.13997483253479</v>
       </c>
-      <c r="G7">
-        <v>304.3</v>
-      </c>
-      <c r="H7">
-        <v>6.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -585,14 +534,8 @@
       <c r="F8">
         <v>12.054036140441889</v>
       </c>
-      <c r="G8">
-        <v>14.62</v>
-      </c>
-      <c r="H8">
-        <v>23.33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>9</v>
       </c>
@@ -611,14 +554,8 @@
       <c r="F9">
         <v>300.59216642379761</v>
       </c>
-      <c r="G9">
-        <v>301.81</v>
-      </c>
-      <c r="H9">
-        <v>306.70999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>10</v>
       </c>
@@ -637,14 +574,8 @@
       <c r="F10">
         <v>302.68493485450739</v>
       </c>
-      <c r="G10">
-        <v>303.14</v>
-      </c>
-      <c r="H10">
-        <v>300.43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>11</v>
       </c>
@@ -663,14 +594,8 @@
       <c r="F11">
         <v>12.036390066146851</v>
       </c>
-      <c r="G11">
-        <v>303.77999999999997</v>
-      </c>
-      <c r="H11">
-        <v>40.369999999999997</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>12</v>
       </c>
@@ -689,14 +614,8 @@
       <c r="F12">
         <v>2.4323608875274658</v>
       </c>
-      <c r="G12">
-        <v>2.61</v>
-      </c>
-      <c r="H12">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>13</v>
       </c>
@@ -715,14 +634,8 @@
       <c r="F13">
         <v>3.5017557144165039</v>
       </c>
-      <c r="G13">
-        <v>4.84</v>
-      </c>
-      <c r="H13">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>14</v>
       </c>
@@ -741,14 +654,8 @@
       <c r="F14">
         <v>2.4344520568847661</v>
       </c>
-      <c r="G14">
-        <v>2.63</v>
-      </c>
-      <c r="H14">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>15</v>
       </c>
@@ -767,14 +674,8 @@
       <c r="F15">
         <v>2.4337477684021001</v>
       </c>
-      <c r="G15">
-        <v>2.61</v>
-      </c>
-      <c r="H15">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>16</v>
       </c>
@@ -793,14 +694,8 @@
       <c r="F16">
         <v>8.2564010620117188</v>
       </c>
-      <c r="G16">
-        <v>7.18</v>
-      </c>
-      <c r="H16">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>17</v>
       </c>
@@ -819,14 +714,8 @@
       <c r="F17">
         <v>305.39624786376947</v>
       </c>
-      <c r="G17">
-        <v>319.89</v>
-      </c>
-      <c r="H17">
-        <v>312.33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>18</v>
       </c>
@@ -845,14 +734,8 @@
       <c r="F18">
         <v>21.812299728393551</v>
       </c>
-      <c r="G18">
-        <v>13.32</v>
-      </c>
-      <c r="H18">
-        <v>20.81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>19</v>
       </c>
@@ -871,14 +754,8 @@
       <c r="F19">
         <v>4.6786377429962158</v>
       </c>
-      <c r="G19">
-        <v>6.05</v>
-      </c>
-      <c r="H19">
-        <v>7.04</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>20</v>
       </c>
@@ -897,14 +774,8 @@
       <c r="F20">
         <v>2.433354377746582</v>
       </c>
-      <c r="G20">
-        <v>2.62</v>
-      </c>
-      <c r="H20">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>21</v>
       </c>
@@ -923,14 +794,8 @@
       <c r="F21">
         <v>18.89876747131348</v>
       </c>
-      <c r="G21">
-        <v>39.85</v>
-      </c>
-      <c r="H21">
-        <v>37.450000000000003</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>22</v>
       </c>
@@ -949,14 +814,8 @@
       <c r="F22">
         <v>2.413902759552002</v>
       </c>
-      <c r="G22">
-        <v>2.59</v>
-      </c>
-      <c r="H22">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>24</v>
       </c>
@@ -975,14 +834,8 @@
       <c r="F23">
         <v>2.4297728538513179</v>
       </c>
-      <c r="G23">
-        <v>2.6</v>
-      </c>
-      <c r="H23">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>26</v>
       </c>
@@ -1001,14 +854,8 @@
       <c r="F24">
         <v>9.9192295074462891</v>
       </c>
-      <c r="G24">
-        <v>305.31</v>
-      </c>
-      <c r="H24">
-        <v>304.26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>27</v>
       </c>
@@ -1027,14 +874,8 @@
       <c r="F25">
         <v>3.4951093196868901</v>
       </c>
-      <c r="G25">
-        <v>4.83</v>
-      </c>
-      <c r="H25">
-        <v>4.6900000000000004</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>28</v>
       </c>
@@ -1053,14 +894,8 @@
       <c r="F26">
         <v>301.32176971435553</v>
       </c>
-      <c r="G26">
-        <v>301.76</v>
-      </c>
-      <c r="H26">
-        <v>301.77999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>29</v>
       </c>
@@ -1079,14 +914,8 @@
       <c r="F27">
         <v>3.506029605865479</v>
       </c>
-      <c r="G27">
-        <v>3.67</v>
-      </c>
-      <c r="H27">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>30</v>
       </c>
@@ -1105,14 +934,8 @@
       <c r="F28">
         <v>21.12445592880249</v>
       </c>
-      <c r="G28">
-        <v>17.88</v>
-      </c>
-      <c r="H28">
-        <v>16.22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>31</v>
       </c>
@@ -1131,14 +954,8 @@
       <c r="F29">
         <v>300.81227779388428</v>
       </c>
-      <c r="G29">
-        <v>302.83</v>
-      </c>
-      <c r="H29">
-        <v>302.81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>32</v>
       </c>
@@ -1157,14 +974,8 @@
       <c r="F30">
         <v>3.492522239685059</v>
       </c>
-      <c r="G30">
-        <v>3.67</v>
-      </c>
-      <c r="H30">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>33</v>
       </c>
@@ -1183,14 +994,8 @@
       <c r="F31">
         <v>3.4968447685241699</v>
       </c>
-      <c r="G31">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="H31">
-        <v>11.77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>34</v>
       </c>
@@ -1209,14 +1014,8 @@
       <c r="F32">
         <v>301.88532519340521</v>
       </c>
-      <c r="G32">
-        <v>303.73</v>
-      </c>
-      <c r="H32">
-        <v>303.42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>35</v>
       </c>
@@ -1235,14 +1034,8 @@
       <c r="F33">
         <v>2.4325695037841801</v>
       </c>
-      <c r="G33">
-        <v>2.6</v>
-      </c>
-      <c r="H33">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>37</v>
       </c>
@@ -1261,14 +1054,8 @@
       <c r="F34">
         <v>3.5039794445037842</v>
       </c>
-      <c r="G34">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="H34">
-        <v>4.63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>38</v>
       </c>
@@ -1287,14 +1074,8 @@
       <c r="F35">
         <v>3.5014734268188481</v>
       </c>
-      <c r="G35">
-        <v>11.34</v>
-      </c>
-      <c r="H35">
-        <v>9.4499999999999993</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>39</v>
       </c>
@@ -1313,14 +1094,8 @@
       <c r="F36">
         <v>2.4384109973907471</v>
       </c>
-      <c r="G36">
-        <v>2.6</v>
-      </c>
-      <c r="H36">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>40</v>
       </c>
@@ -1339,14 +1114,8 @@
       <c r="F37">
         <v>21.824800491333011</v>
       </c>
-      <c r="G37">
-        <v>316.11</v>
-      </c>
-      <c r="H37">
-        <v>50.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>41</v>
       </c>
@@ -1365,14 +1134,8 @@
       <c r="F38">
         <v>9.4579610824584961</v>
       </c>
-      <c r="G38">
-        <v>5.97</v>
-      </c>
-      <c r="H38">
-        <v>10.51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>42</v>
       </c>
@@ -1391,14 +1154,8 @@
       <c r="F39">
         <v>2.4262926578521729</v>
       </c>
-      <c r="G39">
-        <v>2.61</v>
-      </c>
-      <c r="H39">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>43</v>
       </c>
@@ -1417,14 +1174,8 @@
       <c r="F40">
         <v>122.1314616203308</v>
       </c>
-      <c r="G40">
-        <v>302.61</v>
-      </c>
-      <c r="H40">
-        <v>302.67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>44</v>
       </c>
@@ -1443,14 +1194,8 @@
       <c r="F41">
         <v>5.904958963394165</v>
       </c>
-      <c r="G41">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="H41">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>45</v>
       </c>
@@ -1469,14 +1214,8 @@
       <c r="F42">
         <v>2.4209954738616939</v>
       </c>
-      <c r="G42">
-        <v>2.61</v>
-      </c>
-      <c r="H42">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>46</v>
       </c>
@@ -1495,14 +1234,8 @@
       <c r="F43">
         <v>2.4309642314910889</v>
       </c>
-      <c r="G43">
-        <v>2.6</v>
-      </c>
-      <c r="H43">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>47</v>
       </c>
@@ -1521,14 +1254,8 @@
       <c r="F44">
         <v>14.4085259437561</v>
       </c>
-      <c r="G44">
-        <v>102.91</v>
-      </c>
-      <c r="H44">
-        <v>21.71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>49</v>
       </c>
@@ -1547,14 +1274,8 @@
       <c r="F45">
         <v>302.02495074272161</v>
       </c>
-      <c r="G45">
-        <v>300.63</v>
-      </c>
-      <c r="H45">
-        <v>300.77999999999997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>51</v>
       </c>
@@ -1573,14 +1294,8 @@
       <c r="F46">
         <v>312.44052886962891</v>
       </c>
-      <c r="G46">
-        <v>315.94</v>
-      </c>
-      <c r="H46">
-        <v>12.15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>52</v>
       </c>
@@ -1599,14 +1314,8 @@
       <c r="F47">
         <v>58.975839138031013</v>
       </c>
-      <c r="G47">
-        <v>311.52</v>
-      </c>
-      <c r="H47">
-        <v>300.19</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>54</v>
       </c>
@@ -1625,14 +1334,8 @@
       <c r="F48">
         <v>304.52147173881531</v>
       </c>
-      <c r="G48">
-        <v>300.26</v>
-      </c>
-      <c r="H48">
-        <v>309.43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>55</v>
       </c>
@@ -1651,14 +1354,8 @@
       <c r="F49">
         <v>2.4267852306365971</v>
       </c>
-      <c r="G49">
-        <v>2.6</v>
-      </c>
-      <c r="H49">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>56</v>
       </c>
@@ -1677,14 +1374,8 @@
       <c r="F50">
         <v>2.421636581420898</v>
       </c>
-      <c r="G50">
-        <v>2.59</v>
-      </c>
-      <c r="H50">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>61</v>
       </c>
@@ -1703,14 +1394,8 @@
       <c r="F51">
         <v>2.4335284233093262</v>
       </c>
-      <c r="G51">
-        <v>2.6</v>
-      </c>
-      <c r="H51">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>63</v>
       </c>
@@ -1729,14 +1414,8 @@
       <c r="F52">
         <v>4.6784205436706543</v>
       </c>
-      <c r="G52">
-        <v>6.01</v>
-      </c>
-      <c r="H52">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>65</v>
       </c>
@@ -1755,14 +1434,8 @@
       <c r="F53">
         <v>301.24715518951422</v>
       </c>
-      <c r="G53">
-        <v>302.57</v>
-      </c>
-      <c r="H53">
-        <v>301.02999999999997</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>66</v>
       </c>
@@ -1781,14 +1454,8 @@
       <c r="F54">
         <v>3.5335712432861328</v>
       </c>
-      <c r="G54">
-        <v>8.4499999999999993</v>
-      </c>
-      <c r="H54">
-        <v>13.59</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>67</v>
       </c>
@@ -1807,14 +1474,8 @@
       <c r="F55">
         <v>301.76429557800287</v>
       </c>
-      <c r="G55">
-        <v>306</v>
-      </c>
-      <c r="H55">
-        <v>300.49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>68</v>
       </c>
@@ -1833,14 +1494,8 @@
       <c r="F56">
         <v>2.4318337440490718</v>
       </c>
-      <c r="G56">
-        <v>2.61</v>
-      </c>
-      <c r="H56">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>69</v>
       </c>
@@ -1859,14 +1514,8 @@
       <c r="F57">
         <v>303.73140716552729</v>
       </c>
-      <c r="G57">
-        <v>302.89</v>
-      </c>
-      <c r="H57">
-        <v>301.87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>72</v>
       </c>
@@ -1885,14 +1534,8 @@
       <c r="F58">
         <v>301.98901009559631</v>
       </c>
-      <c r="G58">
-        <v>301.43</v>
-      </c>
-      <c r="H58">
-        <v>301.52999999999997</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>73</v>
       </c>
@@ -1911,14 +1554,8 @@
       <c r="F59">
         <v>2.4256594181060791</v>
       </c>
-      <c r="G59">
-        <v>2.59</v>
-      </c>
-      <c r="H59">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>74</v>
       </c>
@@ -1937,14 +1574,8 @@
       <c r="F60">
         <v>2.438174724578857</v>
       </c>
-      <c r="G60">
-        <v>2.6</v>
-      </c>
-      <c r="H60">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>75</v>
       </c>
@@ -1963,14 +1594,8 @@
       <c r="F61">
         <v>3.6605415344238281</v>
       </c>
-      <c r="G61">
-        <v>4.79</v>
-      </c>
-      <c r="H61">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>76</v>
       </c>
@@ -1989,14 +1614,8 @@
       <c r="F62">
         <v>2.4452857971191411</v>
       </c>
-      <c r="G62">
-        <v>2.62</v>
-      </c>
-      <c r="H62">
-        <v>2.4500000000000002</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>77</v>
       </c>
@@ -2015,14 +1634,8 @@
       <c r="F63">
         <v>3.502989530563354</v>
       </c>
-      <c r="G63">
-        <v>5.98</v>
-      </c>
-      <c r="H63">
-        <v>13.09</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>78</v>
       </c>
@@ -2041,14 +1654,8 @@
       <c r="F64">
         <v>300.99695730209351</v>
       </c>
-      <c r="G64">
-        <v>301.77</v>
-      </c>
-      <c r="H64">
-        <v>302.95999999999998</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>79</v>
       </c>
@@ -2067,14 +1674,8 @@
       <c r="F65">
         <v>8.4162392616271973</v>
       </c>
-      <c r="G65">
-        <v>11.15</v>
-      </c>
-      <c r="H65">
-        <v>8.67</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>80</v>
       </c>
@@ -2093,14 +1694,8 @@
       <c r="F66">
         <v>2.4219026565551758</v>
       </c>
-      <c r="G66">
-        <v>2.6</v>
-      </c>
-      <c r="H66">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>81</v>
       </c>
@@ -2119,14 +1714,8 @@
       <c r="F67">
         <v>5.8944327831268311</v>
       </c>
-      <c r="G67">
-        <v>12.04</v>
-      </c>
-      <c r="H67">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>82</v>
       </c>
@@ -2145,14 +1734,8 @@
       <c r="F68">
         <v>2.4252064228057861</v>
       </c>
-      <c r="G68">
-        <v>2.61</v>
-      </c>
-      <c r="H68">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>83</v>
       </c>
@@ -2171,14 +1754,8 @@
       <c r="F69">
         <v>2.42698073387146</v>
       </c>
-      <c r="G69">
-        <v>2.59</v>
-      </c>
-      <c r="H69">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>84</v>
       </c>
@@ -2197,14 +1774,8 @@
       <c r="F70">
         <v>2.4281430244445801</v>
       </c>
-      <c r="G70">
-        <v>2.59</v>
-      </c>
-      <c r="H70">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>85</v>
       </c>
@@ -2223,14 +1794,8 @@
       <c r="F71">
         <v>4.7750446796417236</v>
       </c>
-      <c r="G71">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="H71">
-        <v>8.7899999999999991</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>87</v>
       </c>
@@ -2249,14 +1814,8 @@
       <c r="F72">
         <v>10.61620473861694</v>
       </c>
-      <c r="G72">
-        <v>11.73</v>
-      </c>
-      <c r="H72">
-        <v>14.83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>89</v>
       </c>
@@ -2275,14 +1834,8 @@
       <c r="F73">
         <v>11.98146557807922</v>
       </c>
-      <c r="G73">
-        <v>6.44</v>
-      </c>
-      <c r="H73">
-        <v>7.46</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>90</v>
       </c>
@@ -2301,14 +1854,8 @@
       <c r="F74">
         <v>7.0640022754669189</v>
       </c>
-      <c r="G74">
-        <v>6.08</v>
-      </c>
-      <c r="H74">
-        <v>6.08</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>91</v>
       </c>
@@ -2327,14 +1874,8 @@
       <c r="F75">
         <v>2.418382883071899</v>
       </c>
-      <c r="G75">
-        <v>2.6</v>
-      </c>
-      <c r="H75">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>93</v>
       </c>
@@ -2353,14 +1894,8 @@
       <c r="F76">
         <v>2.423732995986938</v>
       </c>
-      <c r="G76">
-        <v>2.59</v>
-      </c>
-      <c r="H76">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>94</v>
       </c>
@@ -2379,14 +1914,8 @@
       <c r="F77">
         <v>24.57518839836121</v>
       </c>
-      <c r="G77">
-        <v>302.60000000000002</v>
-      </c>
-      <c r="H77">
-        <v>32.840000000000003</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>95</v>
       </c>
@@ -2405,14 +1934,8 @@
       <c r="F78">
         <v>11.97592878341675</v>
       </c>
-      <c r="G78">
-        <v>13.39</v>
-      </c>
-      <c r="H78">
-        <v>16.899999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>96</v>
       </c>
@@ -2431,14 +1954,8 @@
       <c r="F79">
         <v>3.4906318187713619</v>
       </c>
-      <c r="G79">
-        <v>25.48</v>
-      </c>
-      <c r="H79">
-        <v>16.149999999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>97</v>
       </c>
@@ -2457,14 +1974,8 @@
       <c r="F80">
         <v>16.48692679405212</v>
       </c>
-      <c r="G80">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="H80">
-        <v>7.21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>98</v>
       </c>
@@ -2483,14 +1994,8 @@
       <c r="F81">
         <v>4.7492842674255371</v>
       </c>
-      <c r="G81">
-        <v>7.36</v>
-      </c>
-      <c r="H81">
-        <v>7.07</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>99</v>
       </c>
@@ -2509,14 +2014,8 @@
       <c r="F82">
         <v>2.4210512638092041</v>
       </c>
-      <c r="G82">
-        <v>2.6</v>
-      </c>
-      <c r="H82">
-        <v>2.4300000000000002</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>100</v>
       </c>
@@ -2534,12 +2033,6 @@
       </c>
       <c r="F83">
         <v>7.0265963077545166</v>
-      </c>
-      <c r="G83">
-        <v>6.37</v>
-      </c>
-      <c r="H83">
-        <v>6.94</v>
       </c>
     </row>
   </sheetData>
